--- a/cds_files/Baylor_CDS_2023-2024.xlsx
+++ b/cds_files/Baylor_CDS_2023-2024.xlsx
@@ -499,7 +499,7 @@
         <v>0.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0.98</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0.02</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.73</v>
+        <v>0.726</v>
       </c>
     </row>
   </sheetData>
